--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Client</t>
   </si>
@@ -23,10 +23,16 @@
     <t>Tid</t>
   </si>
   <si>
-    <t>BaseHp</t>
-  </si>
-  <si>
-    <t>BaseStamina</t>
+    <t>MaxHp</t>
+  </si>
+  <si>
+    <t>MaxStamina</t>
+  </si>
+  <si>
+    <t>StaminaRegenAmount</t>
+  </si>
+  <si>
+    <t>StaminaRegenDelay</t>
   </si>
   <si>
     <t>WalkSpeed</t>
@@ -41,12 +47,12 @@
     <t>BaseAttack</t>
   </si>
   <si>
+    <t>BaseAttackSpeed</t>
+  </si>
+  <si>
     <t>BaseDefence</t>
   </si>
   <si>
-    <t>BaseAttackSpeed</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -63,6 +69,9 @@
   </si>
   <si>
     <t>가드</t>
+  </si>
+  <si>
+    <t>전력질주</t>
   </si>
   <si>
     <t>구르기</t>
@@ -72,7 +81,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -88,6 +97,11 @@
       <sz val="9.0"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -130,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -145,6 +159,9 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -398,6 +415,12 @@
       <c r="J1" s="1">
         <v>1.0</v>
       </c>
+      <c r="K1" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="L1" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -430,6 +453,12 @@
       <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="K2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3"/>
@@ -440,25 +469,31 @@
         <v>200.0</v>
       </c>
       <c r="D3" s="2">
-        <v>200.0</v>
+        <v>100.0</v>
       </c>
       <c r="E3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G3" s="2">
         <v>100.0</v>
       </c>
-      <c r="F3" s="2">
+      <c r="H3" s="2">
         <v>400.0</v>
       </c>
-      <c r="G3" s="2">
+      <c r="I3" s="2">
         <v>700.0</v>
       </c>
-      <c r="H3" s="2">
-        <v>50.0</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="J3" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="L3" s="2">
         <v>10.0</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -501,16 +536,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +554,7 @@
         <v>10001.0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2">
         <v>0.0</v>
@@ -537,7 +572,7 @@
         <v>10011.0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2">
         <v>1.0</v>
@@ -550,20 +585,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2">
+      <c r="B5" s="5">
+        <v>10020.0</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2">
         <v>10021.0</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2">
         <v>2.0</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E6" s="2">
         <v>0.0</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F6" s="2">
         <v>10.0</v>
       </c>
     </row>

--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Client</t>
   </si>
@@ -56,32 +56,44 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ActionType</t>
-  </si>
-  <si>
-    <t>CoolTime</t>
-  </si>
-  <si>
-    <t>ConsumeStamina</t>
-  </si>
-  <si>
-    <t>기본공격 1타</t>
-  </si>
-  <si>
-    <t>가드</t>
-  </si>
-  <si>
-    <t>전력질주</t>
-  </si>
-  <si>
-    <t>구르기</t>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>StaminaCost</t>
+  </si>
+  <si>
+    <t>MinRequiredStamina</t>
+  </si>
+  <si>
+    <t>LightAttack</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>HeavyAttack</t>
+  </si>
+  <si>
+    <t>Guard</t>
+  </si>
+  <si>
+    <t>Defence</t>
+  </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>Movement</t>
+  </si>
+  <si>
+    <t>DodgeRoll</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -99,12 +111,21 @@
       <name val="&quot;맑은 고딕&quot;"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="9.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="&quot;\0022맑은 고딕\0022&quot;"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;\0022맑은 고딕\0022&quot;"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -115,12 +136,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF595959"/>
         <bgColor rgb="FF595959"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFBFBF"/>
-        <bgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
   </fills>
@@ -144,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -157,11 +172,17 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,116 +528,139 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="5" max="5" width="25.5"/>
+    <col customWidth="1" min="6" max="6" width="27.0"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C1" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="D1" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="E1" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="F1" s="1">
+      <c r="B1" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="C1" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D1" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E1" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F1" s="4">
         <v>1.0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="2">
+      <c r="A3" s="6"/>
+      <c r="B3" s="5">
         <v>10001.0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>5.0</v>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5">
+        <v>10002.0</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="5">
+        <v>30.0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6"/>
+      <c r="B5" s="5">
         <v>10011.0</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="5">
+      <c r="C5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7"/>
+      <c r="B6" s="5">
         <v>10020.0</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="C6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="5">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2">
+      <c r="F6" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6"/>
+      <c r="B7" s="5">
         <v>10021.0</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>10.0</v>
+      <c r="C7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>StaminaRecoveryAmount</t>
+          <t>StaminaRecoveryPerSecond</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -501,7 +501,7 @@
         <v>33.3333333333</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>100</v>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="25.5" customWidth="1" style="8" min="5" max="5"/>
@@ -558,7 +558,13 @@
       <c r="E1" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F1" s="4" t="n">
+      <c r="F1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -588,9 +594,19 @@
           <t>StaminaCost</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>StaminaCostType</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>MinRequiredStamina</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>SprintRestartStaminaPercent</t>
         </is>
       </c>
     </row>
@@ -612,8 +628,16 @@
       <c r="E3" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>1</v>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -634,8 +658,16 @@
       <c r="E4" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="6" t="n">
-        <v>1</v>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -656,8 +688,16 @@
       <c r="E5" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>1</v>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -676,10 +716,18 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>PerSecond</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -700,8 +748,16 @@
       <c r="E7" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>1</v>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -504,7 +504,7 @@
         <v>0.15</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>400</v>

--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -507,7 +507,7 @@
         <v>180</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>700</v>

--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -512,7 +512,7 @@
         <v>33.333333333299997</v>
       </c>
       <c r="F3" s="2">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2">
         <v>180</v>

--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -509,7 +509,7 @@
         <v>100</v>
       </c>
       <c r="E3" s="2">
-        <v>33.333333333299997</v>
+        <v>45</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>

--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -509,10 +509,10 @@
         <v>100</v>
       </c>
       <c r="E3" s="2">
-        <v>33.333333333299997</v>
+        <v>45</v>
       </c>
       <c r="F3" s="2">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2">
         <v>180</v>

--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -1,88 +1,112 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mindo\Workspace\ProjectBA\BADesign\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C8CB4A-3F8C-41EC-9195-DDDD28F60AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="BaseStat" sheetId="1" r:id="rId1"/>
+    <sheet name="BaseStat" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>참고</t>
-  </si>
-  <si>
-    <t>Tid</t>
-  </si>
-  <si>
-    <t>MaxHp</t>
-  </si>
-  <si>
-    <t>MaxStamina</t>
-  </si>
-  <si>
-    <t>StaminaRecoveryPerSecond</t>
-  </si>
-  <si>
-    <t>StaminaRecoveryDelay</t>
-  </si>
-  <si>
-    <t>WalkSpeed</t>
-  </si>
-  <si>
-    <t>RunSpeed</t>
-  </si>
-  <si>
-    <t>SprintSpeed</t>
-  </si>
-  <si>
-    <t>BaseAttack</t>
-  </si>
-  <si>
-    <t>BaseAttackSpeed</t>
-  </si>
-  <si>
-    <t>BaseDefence</t>
-  </si>
-  <si>
-    <t>LadderClimbSpeedSlow</t>
-  </si>
-  <si>
-    <t>LadderClimbSpeedFast</t>
-  </si>
-  <si>
-    <t>LadderSlideDownSpeed</t>
-  </si>
-  <si>
-    <t>LadderExitClearance</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t xml:space="preserve">Client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">참고</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxStamina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StaminaRecoveryPerSecond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StaminaRecoveryDelay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RunSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SprintSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseAttackSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseDefence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LadderClimbSpeedSlow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LadderClimbSpeedFast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LadderSlideDownSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LadderExitClearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HealCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HealAmount</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="9"/>
@@ -98,22 +122,6 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -125,74 +133,138 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF595959"/>
-        <bgColor rgb="FF595959"/>
+        <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF595959"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -234,59 +306,55 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -294,33 +362,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -333,13 +392,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -349,15 +402,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -365,7 +416,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -373,81 +423,88 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr defaultColWidth="11.62109375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="13" max="14" width="21.5546875" customWidth="1"/>
-    <col min="15" max="15" width="21.6640625" customWidth="1"/>
-    <col min="16" max="16" width="18.88671875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="19.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="19.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="17.32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1">
-        <v>1</v>
-      </c>
-      <c r="I1" s="1">
-        <v>1</v>
-      </c>
-      <c r="J1" s="1">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>1</v>
-      </c>
-      <c r="M1" s="1">
-        <v>1</v>
-      </c>
-      <c r="N1" s="1">
-        <v>1</v>
-      </c>
-      <c r="O1" s="1">
-        <v>1</v>
-      </c>
-      <c r="P1" s="1">
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R1" s="1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -496,58 +553,74 @@
       <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="Q2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="K3" s="2">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2">
+      <c r="K3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="2" t="n">
         <v>80</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -92,6 +92,7 @@
       <color rgb="FF000000"/>
       <name val="나눔고딕"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -178,16 +179,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -443,174 +448,174 @@
   <dimension ref="A1:R3"/>
   <sheetFormatPr defaultColWidth="11.62109375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="19.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="19.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="19.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="19.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="17.32"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R1" s="1" t="n">
+      <c r="B1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="n">
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="3" t="n">
         <v>700</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2" t="n">
+      <c r="K3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P3" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="3" t="n">
         <v>25</v>
       </c>
     </row>

--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -616,7 +616,7 @@
         <v>3</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -512,7 +512,7 @@
         <v>45</v>
       </c>
       <c r="F3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
         <v>180</v>

--- a/BADesign/Excel/Player.xlsx
+++ b/BADesign/Excel/Player.xlsx
@@ -1,88 +1,112 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mindo\Workspace\ProjectBA\BADesign\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C8CB4A-3F8C-41EC-9195-DDDD28F60AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="BaseStat" sheetId="1" r:id="rId1"/>
+    <sheet name="BaseStat" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>참고</t>
-  </si>
-  <si>
-    <t>Tid</t>
-  </si>
-  <si>
-    <t>MaxHp</t>
-  </si>
-  <si>
-    <t>MaxStamina</t>
-  </si>
-  <si>
-    <t>StaminaRecoveryPerSecond</t>
-  </si>
-  <si>
-    <t>StaminaRecoveryDelay</t>
-  </si>
-  <si>
-    <t>WalkSpeed</t>
-  </si>
-  <si>
-    <t>RunSpeed</t>
-  </si>
-  <si>
-    <t>SprintSpeed</t>
-  </si>
-  <si>
-    <t>BaseAttack</t>
-  </si>
-  <si>
-    <t>BaseAttackSpeed</t>
-  </si>
-  <si>
-    <t>BaseDefence</t>
-  </si>
-  <si>
-    <t>LadderClimbSpeedSlow</t>
-  </si>
-  <si>
-    <t>LadderClimbSpeedFast</t>
-  </si>
-  <si>
-    <t>LadderSlideDownSpeed</t>
-  </si>
-  <si>
-    <t>LadderExitClearance</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t xml:space="preserve">Client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">참고</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxStamina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StaminaRecoveryPerSecond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StaminaRecoveryDelay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RunSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SprintSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseAttackSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseDefence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LadderClimbSpeedSlow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LadderClimbSpeedFast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LadderSlideDownSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LadderExitClearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HealCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HealAmount</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="9"/>
@@ -93,26 +117,22 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -125,74 +145,146 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF595959"/>
-        <bgColor rgb="FF595959"/>
+        <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  </cellStyleXfs>
+  <cellXfs count="5">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF595959"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -234,59 +326,55 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -294,33 +382,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -333,13 +412,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -349,15 +422,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -365,7 +436,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -373,181 +443,204 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr defaultColWidth="11.62109375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="13" max="14" width="21.5546875" customWidth="1"/>
-    <col min="15" max="15" width="21.6640625" customWidth="1"/>
-    <col min="16" max="16" width="18.88671875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="19.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="19.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="17.32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1">
-        <v>1</v>
-      </c>
-      <c r="I1" s="1">
-        <v>1</v>
-      </c>
-      <c r="J1" s="1">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>1</v>
-      </c>
-      <c r="M1" s="1">
-        <v>1</v>
-      </c>
-      <c r="N1" s="1">
-        <v>1</v>
-      </c>
-      <c r="O1" s="1">
-        <v>1</v>
-      </c>
-      <c r="P1" s="1">
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="Q2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="3" t="n">
         <v>700</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="K3" s="2">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2">
+      <c r="K3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="3" t="n">
         <v>80</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>